--- a/Data/Datos.xlsx
+++ b/Data/Datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancolombia-my.sharepoint.com/personal/damonsal_bancolombia_com_co/Documents/Reto_mundial/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F0979E8-C181-484E-B6B8-B2E0F7A7DB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{3F0979E8-C181-484E-B6B8-B2E0F7A7DB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CD29641-58BA-4A7F-B186-BF95C8EA1EFB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E6CD23CB-0203-4D33-A556-83293F032EFF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E6CD23CB-0203-4D33-A556-83293F032EFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
   <si>
     <t>País</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Colombia</t>
   </si>
   <si>
-    <t>EE. UU.</t>
-  </si>
-  <si>
     <t>México</t>
   </si>
   <si>
@@ -279,6 +276,12 @@
   </si>
   <si>
     <t>N. Caledonia</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>Suecia</t>
   </si>
 </sst>
 </file>
@@ -659,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26175E2B-9E33-4DC9-B50D-D3DF798C76A4}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -1367,9 +1370,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
@@ -1416,7 +1419,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
@@ -1463,7 +1466,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
@@ -1510,7 +1513,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -1557,7 +1560,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>16</v>
@@ -1604,7 +1607,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>16</v>
@@ -1651,7 +1654,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>29</v>
@@ -1698,7 +1701,7 @@
     </row>
     <row r="23" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -1745,7 +1748,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>16</v>
@@ -1792,7 +1795,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>16</v>
@@ -1839,7 +1842,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>29</v>
@@ -1886,7 +1889,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>16</v>
@@ -1933,7 +1936,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>16</v>
@@ -1980,7 +1983,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>16</v>
@@ -2027,7 +2030,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>16</v>
@@ -2074,7 +2077,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>29</v>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>16</v>
@@ -2168,7 +2171,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>16</v>
@@ -2215,7 +2218,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>16</v>
@@ -2262,7 +2265,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>29</v>
@@ -2309,7 +2312,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>29</v>
@@ -2356,7 +2359,7 @@
     </row>
     <row r="37" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>16</v>
@@ -2403,7 +2406,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>16</v>
@@ -2450,7 +2453,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>16</v>
@@ -2497,7 +2500,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>29</v>
@@ -2544,7 +2547,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>29</v>
@@ -2591,7 +2594,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>16</v>
@@ -2638,7 +2641,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>29</v>
@@ -2685,7 +2688,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>29</v>
@@ -2732,7 +2735,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>16</v>
@@ -2779,7 +2782,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>16</v>
@@ -2826,7 +2829,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>29</v>
@@ -2873,7 +2876,7 @@
     </row>
     <row r="48" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>29</v>
@@ -2920,7 +2923,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>16</v>
@@ -2967,7 +2970,7 @@
     </row>
     <row r="50" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>16</v>
@@ -3014,7 +3017,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>29</v>
@@ -3061,7 +3064,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>16</v>
@@ -3108,7 +3111,7 @@
     </row>
     <row r="53" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>29</v>
@@ -3155,7 +3158,7 @@
     </row>
     <row r="54" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>16</v>
@@ -3202,7 +3205,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>29</v>
@@ -3249,7 +3252,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>29</v>
@@ -3296,7 +3299,7 @@
     </row>
     <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>29</v>
@@ -3343,7 +3346,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>16</v>
@@ -3390,7 +3393,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>16</v>
@@ -3437,7 +3440,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>29</v>
@@ -3484,7 +3487,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>29</v>
@@ -3531,7 +3534,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>16</v>
@@ -3578,7 +3581,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>16</v>
@@ -3625,7 +3628,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>29</v>
@@ -3672,7 +3675,7 @@
     </row>
     <row r="65" spans="1:15" ht="28" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>29</v>
@@ -3714,6 +3717,53 @@
         <v>0</v>
       </c>
       <c r="O65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="1">
+        <v>37</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1514.77</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1">
+        <v>13</v>
+      </c>
+      <c r="H66" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="I66" s="1">
+        <v>26.3</v>
+      </c>
+      <c r="J66" s="1">
+        <v>6</v>
+      </c>
+      <c r="K66" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="L66" s="1">
+        <v>4</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="O66" s="1">
         <v>0</v>
       </c>
     </row>
